--- a/ket_qua/ket_qua_modelLinearDiscriminantAnalysis.xlsx
+++ b/ket_qua/ket_qua_modelLinearDiscriminantAnalysis.xlsx
@@ -7,10 +7,10 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Baseline_Comparison" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Confusion Matrix" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KFold" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Baseline_3_Loai_Data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="So_Sanh_Tuning" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Confusion_Matrix_Tuned" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KFold_Tuned" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -484,13 +484,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Validation Accuracy</t>
+          <t>Phiên bản Mô hình</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -500,19 +500,38 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Mean KFold Accuracy</t>
+          <t>Bộ tham số</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>0.74375</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Baseline (Tham số mặc định)</t>
+        </is>
       </c>
       <c r="B2" t="n">
         <v>0.7554585152838428</v>
       </c>
-      <c r="C2" t="n">
-        <v>0.7613906359189377</v>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Mặc định</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Tuned (Đã tinh chỉnh)</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0.7510917030567685</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>{'shrinkage': 'auto', 'solver': 'lsqr'}</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -539,18 +558,18 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B2" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B3" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -564,64 +583,59 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>KFold Scores</t>
+          <t>KFold Mean Scores (All Params)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.7222222222222222</v>
+        <v>0.7613906359189377</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.7407407407407407</v>
+        <v>0.7669461914744933</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.7547169811320755</v>
+        <v>0.7669461914744933</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0.7169811320754716</v>
+        <v>0.7632075471698114</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>0.7547169811320755</v>
+        <v>0.7632075471698114</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0.7358490566037735</v>
+        <v>0.7575471698113206</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>0.7924528301886793</v>
+        <v>0.7575471698113206</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>0.7735849056603774</v>
+        <v>0.7575821104122991</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0.8113207547169812</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>0.8113207547169812</v>
+        <v>0.7575821104122991</v>
       </c>
     </row>
   </sheetData>
